--- a/output/pdf_financials_xlsx/PDFI.xlsx
+++ b/output/pdf_financials_xlsx/PDFI.xlsx
@@ -609,13 +609,13 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.016063</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.030605</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>2.4e-05</v>
       </c>
     </row>
     <row r="13">
@@ -861,13 +861,13 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-1.747883</v>
+        <v>-1.763946</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-2.696047</v>
+        <v>-2.726652</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-2.185454</v>
+        <v>-2.185478</v>
       </c>
     </row>
     <row r="28">
@@ -893,13 +893,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-1.747883</v>
+        <v>-1.763946</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-2.696047</v>
+        <v>-2.726652</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-2.185454</v>
+        <v>-2.185478</v>
       </c>
     </row>
     <row r="30">
@@ -909,13 +909,13 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>-280.0547008437453</v>
+        <v>-282.6283963712223</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>854.6886590878831</v>
+        <v>864.3909181402604</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>-5437.805424234884</v>
+        <v>-5437.865140582235</v>
       </c>
     </row>
     <row r="31">
@@ -6094,7 +6094,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E113" s="5" t="n">

--- a/output/pdf_financials_xlsx/PDFI.xlsx
+++ b/output/pdf_financials_xlsx/PDFI.xlsx
@@ -529,13 +529,13 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.23162</v>
+        <v>0.266968</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.15991</v>
+        <v>0.194759</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.115336</v>
+        <v>0.13951</v>
       </c>
     </row>
     <row r="8">
@@ -6616,7 +6616,11 @@
           <t>Office expenses</t>
         </is>
       </c>
-      <c r="D131" t="inlineStr"/>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E131" s="5" t="n">
         <v>0.035348</v>
       </c>
